--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\Mesophotic_systematic_lit_rev_analysis\Extracted_data_analysis\Input_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\Mesophotic_systematic_lit_rev_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C034507-386F-45A9-9E33-7095CA7035FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2B3F44-FDBC-4F2F-9341-FB72D2EB9BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -1202,7 +1202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1219,19 +1219,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1244,13 +1234,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
@@ -1259,6 +1242,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1540,14 +1538,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" customWidth="1"/>
-    <col min="2" max="3" width="46.21875" style="20" customWidth="1"/>
+    <col min="2" max="3" width="46.21875" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1569,7 +1567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1580,7 +1578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1591,7 +1589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1602,7 +1600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -1613,7 +1611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -1624,7 +1622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1635,7 +1633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1646,7 +1644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
@@ -1657,7 +1655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -1668,23 +1666,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="20" customFormat="1" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:3" s="13" customFormat="1" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:3" s="20" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14" spans="1:3" s="13" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1695,43 +1693,43 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="20" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:3" s="13" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+    <row r="16" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="20" customFormat="1" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:3" s="13" customFormat="1" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+    <row r="18" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="20" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" s="13" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
@@ -1742,37 +1740,37 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="20" customFormat="1" ht="301.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:3" s="13" customFormat="1" ht="301.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+    <row r="21" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="5"/>
     </row>
-    <row r="22" spans="1:3" s="20" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+    <row r="22" spans="1:3" s="13" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="20" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+    <row r="23" spans="1:3" s="13" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="20" customFormat="1" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" s="13" customFormat="1" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>50</v>
       </c>
@@ -1783,75 +1781,75 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="20" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:3" s="13" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+    <row r="26" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+    <row r="27" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+    <row r="28" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="20" customFormat="1" ht="316.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:3" s="13" customFormat="1" ht="316.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+    <row r="30" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="20" customFormat="1" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:3" s="13" customFormat="1" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+    <row r="32" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="20" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" s="13" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>67</v>
       </c>
@@ -1862,53 +1860,53 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="20" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
+    <row r="35" spans="1:3" s="13" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
       <c r="C35" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="20" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
+    <row r="36" spans="1:3" s="13" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
       <c r="C36" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
+    <row r="37" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
+    <row r="38" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="20" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
+    <row r="39" spans="1:3" s="13" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
       <c r="C39" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>77</v>
       </c>
@@ -1919,7 +1917,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="20" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" s="13" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -1930,7 +1928,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="20" customFormat="1" ht="84" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" s="13" customFormat="1" ht="84" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>83</v>
       </c>
@@ -1941,25 +1939,25 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:3" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:3" s="20" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
+    <row r="44" spans="1:3" s="13" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>90</v>
       </c>
@@ -1970,7 +1968,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>92</v>
       </c>
@@ -1981,7 +1979,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>95</v>
       </c>
@@ -1992,7 +1990,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:3" s="20" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" s="13" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>98</v>
       </c>
@@ -2003,7 +2001,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>101</v>
       </c>
@@ -2014,7 +2012,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>103</v>
       </c>
@@ -2025,7 +2023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>105</v>
       </c>
@@ -2036,7 +2034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="20" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" s="13" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>107</v>
       </c>
@@ -2047,7 +2045,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>109</v>
       </c>
@@ -2058,7 +2056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>111</v>
       </c>
@@ -2069,7 +2067,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>113</v>
       </c>
@@ -2080,7 +2078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>115</v>
       </c>
@@ -2091,7 +2089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>117</v>
       </c>
@@ -2102,7 +2100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:3" s="20" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" s="13" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>119</v>
       </c>
@@ -2113,36 +2111,30 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="10"/>
-    </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="10"/>
+      <c r="A60" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="A34:A39"/>
     <mergeCell ref="B34:B39"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2154,198 +2146,198 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="2" width="147.5546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="147.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="12" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="12" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="12" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="12" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="12" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="12" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="12" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="12" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="12" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="12" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="12" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="12" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="12" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="12" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="12" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="12" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="12" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="12" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2363,119 +2355,119 @@
     <col min="2" max="2" width="91.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="15" customFormat="1" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:2" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-    </row>
-    <row r="4" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="12" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="12" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="15" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="12" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="19" t="s">
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="19" t="s">
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" s="15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="12" t="s">
         <v>148</v>
       </c>
     </row>
